--- a/AtchisonRegime/Outputs/Aust/ASX300_Energy/df_regSummary_ASX300_Energy.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Energy/df_regSummary_ASX300_Energy.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8551892799233083</v>
+        <v>0.8190472649359588</v>
       </c>
       <c r="H2" t="n">
-        <v>5.185150853555981</v>
+        <v>5.173799013631518</v>
       </c>
       <c r="I2" t="n">
         <v>-10.7369500066555</v>
@@ -545,19 +545,19 @@
         <v>28.2407194114024</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L2" t="n">
         <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07787199527246416</v>
+        <v>0.07594795450451906</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2241417343000396</v>
+        <v>-0.2472302235153808</v>
       </c>
       <c r="P2" t="n">
         <v>0.3961971237699671</v>
@@ -603,7 +603,7 @@
         <v>10.1238105397411</v>
       </c>
       <c r="K3" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L3" t="n">
         <v>12</v>
@@ -661,7 +661,7 @@
         <v>13.2720975781699</v>
       </c>
       <c r="K4" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>25.211119079268</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L5" t="n">
         <v>12</v>
